--- a/artfynd/A 14545-2025 artfynd.xlsx
+++ b/artfynd/A 14545-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -979,6 +979,342 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>125547338</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Skälsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>599482</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6959600</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>125547357</v>
+      </c>
+      <c r="B6" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Skälsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>599600</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6959534</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>125547227</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97147</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Skälsjön, Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>599477</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6959568</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 14545-2025 artfynd.xlsx
+++ b/artfynd/A 14545-2025 artfynd.xlsx
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125547338</v>
+        <v>125547357</v>
       </c>
       <c r="B5" t="n">
-        <v>98269</v>
+        <v>78947</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,39 +993,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1033,13 +1024,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599482</v>
+        <v>599600</v>
       </c>
       <c r="R5" t="n">
-        <v>6959600</v>
+        <v>6959534</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125547357</v>
+        <v>125547227</v>
       </c>
       <c r="B6" t="n">
-        <v>78947</v>
+        <v>97147</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1108,30 +1099,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1139,13 +1139,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599600</v>
+        <v>599477</v>
       </c>
       <c r="R6" t="n">
-        <v>6959534</v>
+        <v>6959568</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1202,10 +1202,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125547227</v>
+        <v>125547338</v>
       </c>
       <c r="B7" t="n">
-        <v>97147</v>
+        <v>98269</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1214,35 +1214,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>64</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1254,10 +1254,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>599477</v>
+        <v>599482</v>
       </c>
       <c r="R7" t="n">
-        <v>6959568</v>
+        <v>6959600</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>

--- a/artfynd/A 14545-2025 artfynd.xlsx
+++ b/artfynd/A 14545-2025 artfynd.xlsx
@@ -981,42 +981,46 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125547357</v>
+        <v>125547227</v>
       </c>
       <c r="B5" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97202</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1024,13 +1028,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599600</v>
+        <v>599477</v>
       </c>
       <c r="R5" t="n">
-        <v>6959534</v>
+        <v>6959568</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1087,51 +1091,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125547227</v>
+        <v>125547357</v>
       </c>
       <c r="B6" t="n">
-        <v>97147</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1139,13 +1129,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599477</v>
+        <v>599600</v>
       </c>
       <c r="R6" t="n">
-        <v>6959568</v>
+        <v>6959534</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1205,12 +1195,7 @@
         <v>125547338</v>
       </c>
       <c r="B7" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 14545-2025 artfynd.xlsx
+++ b/artfynd/A 14545-2025 artfynd.xlsx
@@ -984,7 +984,7 @@
         <v>125547227</v>
       </c>
       <c r="B5" t="n">
-        <v>97202</v>
+        <v>97209</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         <v>125547338</v>
       </c>
       <c r="B7" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 14545-2025 artfynd.xlsx
+++ b/artfynd/A 14545-2025 artfynd.xlsx
@@ -984,7 +984,7 @@
         <v>125547227</v>
       </c>
       <c r="B5" t="n">
-        <v>97209</v>
+        <v>97212</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>125547357</v>
       </c>
       <c r="B6" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         <v>125547338</v>
       </c>
       <c r="B7" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 14545-2025 artfynd.xlsx
+++ b/artfynd/A 14545-2025 artfynd.xlsx
@@ -984,7 +984,7 @@
         <v>125547227</v>
       </c>
       <c r="B5" t="n">
-        <v>97212</v>
+        <v>97216</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>125547357</v>
       </c>
       <c r="B6" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         <v>125547338</v>
       </c>
       <c r="B7" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 14545-2025 artfynd.xlsx
+++ b/artfynd/A 14545-2025 artfynd.xlsx
@@ -984,7 +984,7 @@
         <v>125547227</v>
       </c>
       <c r="B5" t="n">
-        <v>97216</v>
+        <v>97217</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         <v>125547338</v>
       </c>
       <c r="B7" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 14545-2025 artfynd.xlsx
+++ b/artfynd/A 14545-2025 artfynd.xlsx
@@ -984,7 +984,7 @@
         <v>125547227</v>
       </c>
       <c r="B5" t="n">
-        <v>97217</v>
+        <v>97219</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>125547357</v>
       </c>
       <c r="B6" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         <v>125547338</v>
       </c>
       <c r="B7" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 14545-2025 artfynd.xlsx
+++ b/artfynd/A 14545-2025 artfynd.xlsx
@@ -984,7 +984,7 @@
         <v>125547227</v>
       </c>
       <c r="B5" t="n">
-        <v>97219</v>
+        <v>97221</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         <v>125547338</v>
       </c>
       <c r="B7" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
